--- a/dtm_dashboard/excel_data/keeping_prr/Екатеринбург/Май 2026.xlsx
+++ b/dtm_dashboard/excel_data/keeping_prr/Екатеринбург/Май 2026.xlsx
@@ -23,9 +23,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>Остатки и обороты в тоннах по дням с 01.05.2026 по 05.05.2026</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+  <si>
+    <t>Остатки и обороты в тоннах по дням с 01.05.2026 по 31.05.2026</t>
   </si>
   <si>
     <t>Отбор:</t>
@@ -65,6 +65,84 @@
   </si>
   <si>
     <t>05.05.2026</t>
+  </si>
+  <si>
+    <t>06.05.2026</t>
+  </si>
+  <si>
+    <t>07.05.2026</t>
+  </si>
+  <si>
+    <t>08.05.2026</t>
+  </si>
+  <si>
+    <t>09.05.2026</t>
+  </si>
+  <si>
+    <t>10.05.2026</t>
+  </si>
+  <si>
+    <t>11.05.2026</t>
+  </si>
+  <si>
+    <t>12.05.2026</t>
+  </si>
+  <si>
+    <t>13.05.2026</t>
+  </si>
+  <si>
+    <t>14.05.2026</t>
+  </si>
+  <si>
+    <t>15.05.2026</t>
+  </si>
+  <si>
+    <t>16.05.2026</t>
+  </si>
+  <si>
+    <t>17.05.2026</t>
+  </si>
+  <si>
+    <t>18.05.2026</t>
+  </si>
+  <si>
+    <t>19.05.2026</t>
+  </si>
+  <si>
+    <t>20.05.2026</t>
+  </si>
+  <si>
+    <t>21.05.2026</t>
+  </si>
+  <si>
+    <t>22.05.2026</t>
+  </si>
+  <si>
+    <t>23.05.2026</t>
+  </si>
+  <si>
+    <t>24.05.2026</t>
+  </si>
+  <si>
+    <t>25.05.2026</t>
+  </si>
+  <si>
+    <t>26.05.2026</t>
+  </si>
+  <si>
+    <t>27.05.2026</t>
+  </si>
+  <si>
+    <t>28.05.2026</t>
+  </si>
+  <si>
+    <t>29.05.2026</t>
+  </si>
+  <si>
+    <t>30.05.2026</t>
+  </si>
+  <si>
+    <t>31.05.2026</t>
   </si>
   <si>
     <t>Итого</t>
@@ -74,11 +152,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="50" formatCode=""/>
     <numFmt numFmtId="51" formatCode="0.000"/>
     <numFmt numFmtId="52" formatCode="#,##0.000"/>
     <numFmt numFmtId="53" formatCode="0.0"/>
+    <numFmt numFmtId="54" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -261,22 +340,22 @@
     <xf numFmtId="2" borderId="2" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="top" wrapText="0"/>
     </xf>
+    <xf numFmtId="1" borderId="2" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="top" wrapText="0"/>
+    </xf>
+    <xf numFmtId="53" borderId="2" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="top" wrapText="0"/>
+    </xf>
     <xf numFmtId="4" borderId="2" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="top" wrapText="0"/>
     </xf>
-    <xf numFmtId="1" borderId="2" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="top" wrapText="0"/>
-    </xf>
-    <xf numFmtId="53" borderId="2" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="top" wrapText="0"/>
-    </xf>
     <xf fontId="3" fillId="2" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="52" fontId="3" fillId="2" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="4" fontId="3" fillId="2" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="top" wrapText="0"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="54" fontId="3" fillId="2" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="top" wrapText="0"/>
     </xf>
     <xf fontId="3" fillId="2" borderId="5" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -307,15 +386,15 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false" fitToPage="false"/>
   </sheetPr>
-  <dimension ref="J12"/>
+  <dimension ref="J38"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="8.66796875" style="1" customWidth="true"/>
     <col min="2" max="2" width="1.83203125" style="1" customWidth="true"/>
     <col min="3" max="3" width="3.5" style="1" customWidth="true"/>
-    <col min="4" max="4" width="12.33203125" style="1" customWidth="true"/>
+    <col min="4" max="4" width="11.16796875" style="1" customWidth="true"/>
     <col min="5" max="5" width="10.83203125" style="1" customWidth="true"/>
-    <col min="6" max="6" width="4" style="1" customWidth="true"/>
+    <col min="6" max="6" width="5.16796875" style="1" customWidth="true"/>
     <col min="7" max="7" width="8.83203125" style="1" customWidth="true"/>
     <col min="8" max="8" width="19.33203125" style="1" customWidth="true"/>
     <col min="9" max="9" width="0.83203125" style="1" customWidth="true"/>
@@ -419,13 +498,13 @@
       <c r="B9" s="5" t="e"/>
       <c r="C9" s="5" t="e"/>
       <c r="D9" s="6" t="n">
-        <v>764.994</v>
+        <v>771.869</v>
       </c>
       <c r="E9" s="7" t="e"/>
-      <c r="F9" s="12" t="n">
-        <v>8212.84</v>
-      </c>
-      <c r="G9" s="12" t="e"/>
+      <c r="F9" s="8" t="n">
+        <v>8219.715</v>
+      </c>
+      <c r="G9" s="8" t="e"/>
       <c r="H9" s="7" t="e"/>
       <c r="I9" s="9" t="e"/>
       <c r="J9" s="10" t="e"/>
@@ -439,11 +518,11 @@
       <c r="D10" s="6" t="n">
         <v>708.013</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="12" t="n">
         <v>45</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>8875.853</v>
+        <v>8882.728</v>
       </c>
       <c r="G10" s="8" t="e"/>
       <c r="H10" s="6" t="n">
@@ -461,43 +540,571 @@
       <c r="B11" s="5" t="e"/>
       <c r="C11" s="5" t="e"/>
       <c r="D11" s="6" t="n">
-        <v>359.484</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>22.5</v>
+        <v>873.483</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>67.5</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>9212.837</v>
+        <v>9688.711</v>
       </c>
       <c r="G11" s="8" t="e"/>
       <c r="H11" s="7" t="e"/>
       <c r="I11" s="9" t="e"/>
       <c r="J11" s="10" t="e"/>
     </row>
-    <row r="12" ht="13" customHeight="true">
-      <c r="A12" s="15" t="s">
+    <row r="12" ht="11" customHeight="true">
+      <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="15" t="e"/>
-      <c r="C12" s="15" t="e"/>
-      <c r="D12" s="16" t="n">
-        <v>2882.663</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>71.75</v>
-      </c>
-      <c r="F12" s="18" t="e"/>
-      <c r="G12" s="19" t="e"/>
-      <c r="H12" s="20" t="n">
-        <v>4.175</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>4.175</v>
-      </c>
-      <c r="J12" s="20" t="e"/>
+      <c r="B12" s="5" t="e"/>
+      <c r="C12" s="5" t="e"/>
+      <c r="D12" s="11" t="n">
+        <v>470.85</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>260.75</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>9898.811</v>
+      </c>
+      <c r="G12" s="8" t="e"/>
+      <c r="H12" s="7" t="e"/>
+      <c r="I12" s="9" t="e"/>
+      <c r="J12" s="10" t="e"/>
+    </row>
+    <row r="13" ht="11" customHeight="true">
+      <c r="A13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="5" t="e"/>
+      <c r="C13" s="5" t="e"/>
+      <c r="D13" s="6" t="n">
+        <v>599.141</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>45.05</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>10452.902</v>
+      </c>
+      <c r="G13" s="8" t="e"/>
+      <c r="H13" s="6" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="J13" s="6" t="e"/>
+    </row>
+    <row r="14" ht="11" customHeight="true">
+      <c r="A14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="5" t="e"/>
+      <c r="C14" s="5" t="e"/>
+      <c r="D14" s="6" t="n">
+        <v>62.874</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>153.875</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>10361.901</v>
+      </c>
+      <c r="G14" s="8" t="e"/>
+      <c r="H14" s="13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J14" s="13" t="e"/>
+    </row>
+    <row r="15" ht="11" customHeight="true">
+      <c r="A15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="5" t="e"/>
+      <c r="C15" s="5" t="e"/>
+      <c r="D15" s="11" t="n">
+        <v>166.22</v>
+      </c>
+      <c r="E15" s="7" t="e"/>
+      <c r="F15" s="8" t="n">
+        <v>10528.121</v>
+      </c>
+      <c r="G15" s="8" t="e"/>
+      <c r="H15" s="7" t="e"/>
+      <c r="I15" s="9" t="e"/>
+      <c r="J15" s="10" t="e"/>
+    </row>
+    <row r="16" ht="11" customHeight="true">
+      <c r="A16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="5" t="e"/>
+      <c r="C16" s="5" t="e"/>
+      <c r="D16" s="11" t="n">
+        <v>86.96</v>
+      </c>
+      <c r="E16" s="7" t="e"/>
+      <c r="F16" s="8" t="n">
+        <v>10615.081</v>
+      </c>
+      <c r="G16" s="8" t="e"/>
+      <c r="H16" s="7" t="e"/>
+      <c r="I16" s="9" t="e"/>
+      <c r="J16" s="10" t="e"/>
+    </row>
+    <row r="17" ht="11" customHeight="true">
+      <c r="A17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="5" t="e"/>
+      <c r="C17" s="5" t="e"/>
+      <c r="D17" s="6" t="n">
+        <v>181.314</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>10751.895</v>
+      </c>
+      <c r="G17" s="8" t="e"/>
+      <c r="H17" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J17" s="13" t="e"/>
+    </row>
+    <row r="18" ht="11" customHeight="true">
+      <c r="A18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="5" t="e"/>
+      <c r="C18" s="5" t="e"/>
+      <c r="D18" s="13" t="n">
+        <v>576.2</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>11260.595</v>
+      </c>
+      <c r="G18" s="8" t="e"/>
+      <c r="H18" s="7" t="e"/>
+      <c r="I18" s="9" t="e"/>
+      <c r="J18" s="10" t="e"/>
+    </row>
+    <row r="19" ht="11" customHeight="true">
+      <c r="A19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="5" t="e"/>
+      <c r="C19" s="5" t="e"/>
+      <c r="D19" s="12" t="n">
+        <v>819</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>12012.095</v>
+      </c>
+      <c r="G19" s="8" t="e"/>
+      <c r="H19" s="7" t="e"/>
+      <c r="I19" s="9" t="e"/>
+      <c r="J19" s="10" t="e"/>
+    </row>
+    <row r="20" ht="11" customHeight="true">
+      <c r="A20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="5" t="e"/>
+      <c r="C20" s="5" t="e"/>
+      <c r="D20" s="6" t="n">
+        <v>899.991</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>12793.586</v>
+      </c>
+      <c r="G20" s="8" t="e"/>
+      <c r="H20" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J20" s="13" t="e"/>
+    </row>
+    <row r="21" ht="11" customHeight="true">
+      <c r="A21" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="5" t="e"/>
+      <c r="C21" s="5" t="e"/>
+      <c r="D21" s="11" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>12894.586</v>
+      </c>
+      <c r="G21" s="8" t="e"/>
+      <c r="H21" s="7" t="e"/>
+      <c r="I21" s="9" t="e"/>
+      <c r="J21" s="10" t="e"/>
+    </row>
+    <row r="22" ht="11" customHeight="true">
+      <c r="A22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="5" t="e"/>
+      <c r="C22" s="5" t="e"/>
+      <c r="D22" s="6" t="n">
+        <v>147.445</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>12862.031</v>
+      </c>
+      <c r="G22" s="8" t="e"/>
+      <c r="H22" s="7" t="e"/>
+      <c r="I22" s="9" t="e"/>
+      <c r="J22" s="10" t="e"/>
+    </row>
+    <row r="23" ht="11" customHeight="true">
+      <c r="A23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="5" t="e"/>
+      <c r="C23" s="5" t="e"/>
+      <c r="D23" s="6" t="n">
+        <v>142.479</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>12937.01</v>
+      </c>
+      <c r="G23" s="14" t="e"/>
+      <c r="H23" s="7" t="e"/>
+      <c r="I23" s="9" t="e"/>
+      <c r="J23" s="10" t="e"/>
+    </row>
+    <row r="24" ht="11" customHeight="true">
+      <c r="A24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="5" t="e"/>
+      <c r="C24" s="5" t="e"/>
+      <c r="D24" s="6" t="n">
+        <v>107.906</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>12989.416</v>
+      </c>
+      <c r="G24" s="8" t="e"/>
+      <c r="H24" s="7" t="e"/>
+      <c r="I24" s="9" t="e"/>
+      <c r="J24" s="10" t="e"/>
+    </row>
+    <row r="25" ht="11" customHeight="true">
+      <c r="A25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="5" t="e"/>
+      <c r="C25" s="5" t="e"/>
+      <c r="D25" s="11" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>12859.266</v>
+      </c>
+      <c r="G25" s="8" t="e"/>
+      <c r="H25" s="7" t="e"/>
+      <c r="I25" s="9" t="e"/>
+      <c r="J25" s="10" t="e"/>
+    </row>
+    <row r="26" ht="11" customHeight="true">
+      <c r="A26" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="5" t="e"/>
+      <c r="C26" s="5" t="e"/>
+      <c r="D26" s="7" t="e"/>
+      <c r="E26" s="11" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>12766.516</v>
+      </c>
+      <c r="G26" s="8" t="e"/>
+      <c r="H26" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J26" s="13" t="e"/>
+    </row>
+    <row r="27" ht="11" customHeight="true">
+      <c r="A27" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="5" t="e"/>
+      <c r="C27" s="5" t="e"/>
+      <c r="D27" s="7" t="e"/>
+      <c r="E27" s="13" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>12577.016</v>
+      </c>
+      <c r="G27" s="8" t="e"/>
+      <c r="H27" s="7" t="e"/>
+      <c r="I27" s="9" t="e"/>
+      <c r="J27" s="10" t="e"/>
+    </row>
+    <row r="28" ht="11" customHeight="true">
+      <c r="A28" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="5" t="e"/>
+      <c r="C28" s="5" t="e"/>
+      <c r="D28" s="7" t="e"/>
+      <c r="E28" s="13" t="n">
+        <v>205.7</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>12371.316</v>
+      </c>
+      <c r="G28" s="8" t="e"/>
+      <c r="H28" s="7" t="e"/>
+      <c r="I28" s="9" t="e"/>
+      <c r="J28" s="10" t="e"/>
+    </row>
+    <row r="29" ht="11" customHeight="true">
+      <c r="A29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="5" t="e"/>
+      <c r="C29" s="5" t="e"/>
+      <c r="D29" s="7" t="e"/>
+      <c r="E29" s="12" t="n">
+        <v>270</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>12101.316</v>
+      </c>
+      <c r="G29" s="8" t="e"/>
+      <c r="H29" s="7" t="e"/>
+      <c r="I29" s="9" t="e"/>
+      <c r="J29" s="10" t="e"/>
+    </row>
+    <row r="30" ht="11" customHeight="true">
+      <c r="A30" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="5" t="e"/>
+      <c r="C30" s="5" t="e"/>
+      <c r="D30" s="11" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>266.5</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>11854.066</v>
+      </c>
+      <c r="G30" s="8" t="e"/>
+      <c r="H30" s="7" t="e"/>
+      <c r="I30" s="9" t="e"/>
+      <c r="J30" s="10" t="e"/>
+    </row>
+    <row r="31" ht="11" customHeight="true">
+      <c r="A31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="5" t="e"/>
+      <c r="C31" s="5" t="e"/>
+      <c r="D31" s="6" t="n">
+        <v>4.481</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>11540.047</v>
+      </c>
+      <c r="G31" s="8" t="e"/>
+      <c r="H31" s="11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J31" s="11" t="e"/>
+    </row>
+    <row r="32" ht="11" customHeight="true">
+      <c r="A32" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="5" t="e"/>
+      <c r="C32" s="5" t="e"/>
+      <c r="D32" s="6" t="n">
+        <v>4.116</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>323.4</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>11220.763</v>
+      </c>
+      <c r="G32" s="8" t="e"/>
+      <c r="H32" s="7" t="e"/>
+      <c r="I32" s="9" t="e"/>
+      <c r="J32" s="10" t="e"/>
+    </row>
+    <row r="33" ht="11" customHeight="true">
+      <c r="A33" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="5" t="e"/>
+      <c r="C33" s="5" t="e"/>
+      <c r="D33" s="7" t="e"/>
+      <c r="E33" s="6" t="n">
+        <v>46.675</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>11174.088</v>
+      </c>
+      <c r="G33" s="8" t="e"/>
+      <c r="H33" s="7" t="e"/>
+      <c r="I33" s="9" t="e"/>
+      <c r="J33" s="10" t="e"/>
+    </row>
+    <row r="34" ht="11" customHeight="true">
+      <c r="A34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="5" t="e"/>
+      <c r="C34" s="5" t="e"/>
+      <c r="D34" s="6" t="n">
+        <v>32.076</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>10923.664</v>
+      </c>
+      <c r="G34" s="8" t="e"/>
+      <c r="H34" s="7" t="e"/>
+      <c r="I34" s="9" t="e"/>
+      <c r="J34" s="10" t="e"/>
+    </row>
+    <row r="35" ht="11" customHeight="true">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="e"/>
+      <c r="C35" s="5" t="e"/>
+      <c r="D35" s="6" t="n">
+        <v>43.614</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>251</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>10716.278</v>
+      </c>
+      <c r="G35" s="8" t="e"/>
+      <c r="H35" s="7" t="e"/>
+      <c r="I35" s="9" t="e"/>
+      <c r="J35" s="10" t="e"/>
+    </row>
+    <row r="36" ht="11" customHeight="true">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="e"/>
+      <c r="C36" s="5" t="e"/>
+      <c r="D36" s="6" t="n">
+        <v>7.026</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>526.5</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>10196.804</v>
+      </c>
+      <c r="G36" s="8" t="e"/>
+      <c r="H36" s="7" t="e"/>
+      <c r="I36" s="9" t="e"/>
+      <c r="J36" s="10" t="e"/>
+    </row>
+    <row r="37" ht="11" customHeight="true">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="e"/>
+      <c r="C37" s="5" t="e"/>
+      <c r="D37" s="7" t="e"/>
+      <c r="E37" s="13" t="n">
+        <v>478.5</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>9718.304</v>
+      </c>
+      <c r="G37" s="8" t="e"/>
+      <c r="H37" s="7" t="e"/>
+      <c r="I37" s="9" t="e"/>
+      <c r="J37" s="10" t="e"/>
+    </row>
+    <row r="38" ht="13" customHeight="true">
+      <c r="A38" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="15" t="e"/>
+      <c r="C38" s="15" t="e"/>
+      <c r="D38" s="16" t="n">
+        <v>7981.58</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>4665.2</v>
+      </c>
+      <c r="F38" s="18" t="e"/>
+      <c r="G38" s="19" t="e"/>
+      <c r="H38" s="20" t="n">
+        <v>27.971</v>
+      </c>
+      <c r="I38" s="20" t="n">
+        <v>27.971</v>
+      </c>
+      <c r="J38" s="20" t="e"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="74">
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="I6:J6"/>
@@ -513,7 +1120,65 @@
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <pageMargins left="0.393700787401574803149606299" top="0.393700787401574803149606299" right="0.393700787401574803149606299" bottom="0.393700787401574803149606299" header="0" footer="0"/>
   <pageSetup blackAndWhite="false" scale="100" pageOrder="overThenDown" orientation="portrait"/>
